--- a/output/pdf_financials_xlsx/TWEL.xlsx
+++ b/output/pdf_financials_xlsx/TWEL.xlsx
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.17171</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.840802</v>
       </c>
     </row>
     <row r="93">
@@ -2654,7 +2654,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.17171</v>
       </c>

--- a/output/pdf_financials_xlsx/TWEL.xlsx
+++ b/output/pdf_financials_xlsx/TWEL.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.05087</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.331991</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.05087</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.02875</v>
+        <v>0.360741</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.078416</v>
+        <v>0.027546</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.56512</v>
+        <v>0.233129</v>
       </c>
     </row>
     <row r="49">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/TWEL.xlsx
+++ b/output/pdf_financials_xlsx/TWEL.xlsx
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005549</v>
       </c>
     </row>
     <row r="112">
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005549</v>
       </c>
     </row>
     <row r="135">
@@ -3086,7 +3086,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
